--- a/submission/DE-FY2026Q3.xlsx
+++ b/submission/DE-FY2026Q3.xlsx
@@ -704,7 +704,7 @@
         </is>
       </c>
       <c r="C9" s="53" t="n">
-        <v>548</v>
+        <v>551</v>
       </c>
     </row>
     <row r="10"/>

--- a/submission/DE-FY2026Q3.xlsx
+++ b/submission/DE-FY2026Q3.xlsx
@@ -689,7 +689,7 @@
         </is>
       </c>
       <c r="C8" s="54" t="n">
-        <v>4.49</v>
+        <v>4.66</v>
       </c>
     </row>
     <row r="9" ht="29" customHeight="1">
